--- a/output/pdf_financials_xlsx/FEX.xlsx
+++ b/output/pdf_financials_xlsx/FEX.xlsx
@@ -6258,28 +6258,28 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.259911</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.258489</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.274876</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.308108</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.614915</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.88867</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.757228</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.792571</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -14638,7 +14638,11 @@
           <t>Share-based Payments Reserve</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FEX.xlsx
+++ b/output/pdf_financials_xlsx/FEX.xlsx
@@ -1059,25 +1059,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.013323</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002535</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00108</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000324</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000119</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00084</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.00024</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2076,25 +2076,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.713358</v>
+        <v>-0.726681</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.803508</v>
+        <v>-0.806043</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.539601</v>
+        <v>-0.540681</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.058336</v>
+        <v>-1.05866</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.354108</v>
+        <v>-0.354227</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.098068</v>
+        <v>-1.098908</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.293519</v>
+        <v>-0.293759</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.32381</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.713358</v>
+        <v>-0.726681</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.803508</v>
+        <v>-0.806043</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.537422</v>
+        <v>-0.538502</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.056698</v>
+        <v>-1.057022</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.351283</v>
+        <v>-0.351402</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.095658</v>
+        <v>-1.096498</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.293519</v>
+        <v>-0.293759</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.322605</v>
@@ -2521,58 +2521,58 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.129152</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.297052</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.297052</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.593153</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.046685</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.10504</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.18646</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.007055</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.204394</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.029097</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.800082</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.685964</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.31069</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.725697</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.894607</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.894607</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.247706</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.042729</v>
       </c>
     </row>
     <row r="35">
@@ -2643,58 +2643,58 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.129152</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.297052</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.297052</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.593153</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.046685</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.10504</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.18646</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.007055</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.204394</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.029097</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.800082</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.685964</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.31069</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.725697</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.894607</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.894607</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.247706</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.042729</v>
       </c>
     </row>
     <row r="37">
@@ -3375,58 +3375,58 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.141817</v>
+        <v>0.012665</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.308368</v>
+        <v>0.011316</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.308368</v>
+        <v>0.011316</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.597395</v>
+        <v>0.004242</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.050971</v>
+        <v>0.004286</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.107495</v>
+        <v>0.002455</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.187152</v>
+        <v>0.000692</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.007191</v>
+        <v>0.000136</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.204533</v>
+        <v>0.000139</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.049575</v>
+        <v>0.020478</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.800233</v>
+        <v>0.000151</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.686119</v>
+        <v>0.000155</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.310845</v>
+        <v>0.000155</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.730114</v>
+        <v>0.004417</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.901708</v>
+        <v>0.007101</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.901708</v>
+        <v>0.007101</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.250817</v>
+        <v>0.003111</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.042729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8256,22 +8256,22 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.02346</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.03006</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.04326</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.04326</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.04326</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.02884</v>
       </c>
       <c r="S124" s="3" t="n">
         <v>0</v>
@@ -8319,22 +8319,22 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.02346</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.03006</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.04326</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.04326</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.04326</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.02884</v>
       </c>
       <c r="S125" s="3" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -20152,7 +20152,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -21722,7 +21726,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -27270,7 +27278,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -38110,7 +38122,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E280" s="5" t="n">
         <v>0.004671</v>
       </c>
@@ -47074,7 +47090,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -48222,7 +48238,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -49182,7 +49198,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E388" s="5" t="n">
